--- a/data/processed/positivacao/2024-11_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2024-11_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26323,7 +26323,7 @@
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr"/>
@@ -37597,7 +37597,7 @@
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1434" t="inlineStr"/>
@@ -65917,7 +65917,7 @@
     <row r="2524">
       <c r="A2524" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2524" t="inlineStr"/>
@@ -67536,12 +67536,12 @@
       <c r="A2587" t="inlineStr"/>
       <c r="B2587" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 8 cliente(s), não positivou 88 cliente(s) - Total vendido: R$ 7.315,73
+          <t>Vendedor 1 - VENDEDOR 01: positivou 8 cliente(s), não positivou 88 cliente(s) - Total vendido: R$ 7.315,73
 Vendedor 18 - LOJA: positivou 199 cliente(s), não positivou 695 cliente(s) - Total vendido: R$ 78.215,75
-Vendedor 3 - FERNANDA: positivou 115 cliente(s), não positivou 318 cliente(s) - Total vendido: R$ 160.212,51
-Vendedor 4 - DANIELA: positivou 107 cliente(s), não positivou 533 cliente(s) - Total vendido: R$ 75.886,48
+Vendedor 3 - VENDEDOR 03: positivou 115 cliente(s), não positivou 318 cliente(s) - Total vendido: R$ 160.212,51
+Vendedor 4 - VENDEDOR 04: positivou 107 cliente(s), não positivou 533 cliente(s) - Total vendido: R$ 75.886,48
 Vendedor 5 - SITE: positivou 2 cliente(s), não positivou 446 cliente(s) - Total vendido: R$ 385,33
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2587" t="inlineStr"/>
